--- a/数据表/Level.xlsx
+++ b/数据表/Level.xlsx
@@ -40,7 +40,7 @@
     <t>Id</t>
   </si>
   <si>
-    <t>EntityIds</t>
+    <t>EnemyTypes</t>
   </si>
   <si>
     <t>EntityCounts</t>
@@ -67,7 +67,7 @@
     <t>策划备注</t>
   </si>
   <si>
-    <t>实体编号</t>
+    <t>敌人类型</t>
   </si>
   <si>
     <t>每次出怪数量</t>
@@ -82,7 +82,7 @@
     <t>第一关</t>
   </si>
   <si>
-    <t>[101]</t>
+    <t>[1]</t>
   </si>
   <si>
     <t>[5]</t>

--- a/数据表/Level.xlsx
+++ b/数据表/Level.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="32">
   <si>
     <t>#</t>
   </si>
@@ -82,16 +82,19 @@
     <t>第一关</t>
   </si>
   <si>
+    <t>[1,2]</t>
+  </si>
+  <si>
+    <t>[5,2]</t>
+  </si>
+  <si>
+    <t>[4,5]</t>
+  </si>
+  <si>
+    <t>第二关</t>
+  </si>
+  <si>
     <t>[1]</t>
-  </si>
-  <si>
-    <t>[5]</t>
-  </si>
-  <si>
-    <t>[2]</t>
-  </si>
-  <si>
-    <t>第二关</t>
   </si>
   <si>
     <t>[10]</t>
@@ -1165,13 +1168,13 @@
         <v>20</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G6" s="1">
         <v>60</v>
@@ -1182,16 +1185,16 @@
         <v>3</v>
       </c>
       <c r="C7" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F7" s="1" t="s">
         <v>23</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>22</v>
       </c>
       <c r="G7" s="1">
         <v>60</v>
@@ -1202,16 +1205,16 @@
         <v>4</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G8" s="1">
         <v>60</v>
@@ -1222,16 +1225,16 @@
         <v>5</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G9" s="1">
         <v>60</v>
@@ -1242,16 +1245,16 @@
         <v>6</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G10" s="1">
         <v>60</v>
@@ -1262,16 +1265,16 @@
         <v>7</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G11" s="1">
         <v>60</v>
@@ -1282,16 +1285,16 @@
         <v>8</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G12" s="1">
         <v>60</v>
@@ -1302,16 +1305,16 @@
         <v>9</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G13" s="1">
         <v>60</v>
@@ -1322,16 +1325,16 @@
         <v>10</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G14" s="1">
         <v>60</v>
